--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98163</v>
+        <v>98166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98163</v>
+        <v>98166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96327</v>
+        <v>96330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98166</v>
+        <v>98174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98166</v>
+        <v>98174</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96330</v>
+        <v>96338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98174</v>
+        <v>98184</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98174</v>
+        <v>98184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96338</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98184</v>
+        <v>98185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98184</v>
+        <v>98185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98185</v>
+        <v>98186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98185</v>
+        <v>98186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96349</v>
+        <v>96350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98186</v>
+        <v>98187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98186</v>
+        <v>98187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96350</v>
+        <v>96351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98187</v>
+        <v>98189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98187</v>
+        <v>98189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96351</v>
+        <v>96353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 60875-2023 artfynd.xlsx
+++ b/artfynd/A 60875-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113682743</v>
       </c>
       <c r="B2" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113682744</v>
       </c>
       <c r="B3" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113678102</v>
       </c>
       <c r="B4" t="n">
-        <v>96353</v>
+        <v>96354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
